--- a/artfynd/A 18032-2022 artfynd.xlsx
+++ b/artfynd/A 18032-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 18032-2022 artfynd.xlsx
+++ b/artfynd/A 18032-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -794,6 +794,336 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>128329026</v>
+      </c>
+      <c r="B3" t="n">
+        <v>101779</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>221343</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Brunklöver</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Trifolium spadiceum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Artrik vägkant, Jmt</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>433249</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7060239</v>
+      </c>
+      <c r="S3" t="n">
+        <v>50</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>NorraInneslänt (IS)Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Magnus Stenmark</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Magnus Stenmark</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>128329027</v>
+      </c>
+      <c r="B4" t="n">
+        <v>101779</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221343</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Brunklöver</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Trifolium spadiceum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Artrik vägkant, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>433234</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7060236</v>
+      </c>
+      <c r="S4" t="n">
+        <v>50</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>NorraInneslänt (IS)Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Magnus Stenmark</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Magnus Stenmark</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128325826</v>
+      </c>
+      <c r="B5" t="n">
+        <v>98475</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Artrik vägkant, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>433237</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7060234</v>
+      </c>
+      <c r="S5" t="n">
+        <v>50</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>NorraInneslänt (IS)Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Magnus Stenmark</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Magnus Stenmark</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
         <is>
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>

--- a/artfynd/A 18032-2022 artfynd.xlsx
+++ b/artfynd/A 18032-2022 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>128329026</v>
       </c>
       <c r="B3" t="n">
-        <v>101779</v>
+        <v>101784</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>128329027</v>
       </c>
       <c r="B4" t="n">
-        <v>101779</v>
+        <v>101784</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>128325826</v>
       </c>
       <c r="B5" t="n">
-        <v>98475</v>
+        <v>98480</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 18032-2022 artfynd.xlsx
+++ b/artfynd/A 18032-2022 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>128329026</v>
       </c>
       <c r="B3" t="n">
-        <v>101784</v>
+        <v>101877</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>128329027</v>
       </c>
       <c r="B4" t="n">
-        <v>101784</v>
+        <v>101877</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>128325826</v>
       </c>
       <c r="B5" t="n">
-        <v>98480</v>
+        <v>98573</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 18032-2022 artfynd.xlsx
+++ b/artfynd/A 18032-2022 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>128329026</v>
       </c>
       <c r="B3" t="n">
-        <v>101877</v>
+        <v>101893</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>128329027</v>
       </c>
       <c r="B4" t="n">
-        <v>101877</v>
+        <v>101893</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>128325826</v>
       </c>
       <c r="B5" t="n">
-        <v>98573</v>
+        <v>98587</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 18032-2022 artfynd.xlsx
+++ b/artfynd/A 18032-2022 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>128329026</v>
       </c>
       <c r="B3" t="n">
-        <v>101893</v>
+        <v>101898</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>128329027</v>
       </c>
       <c r="B4" t="n">
-        <v>101893</v>
+        <v>101898</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>128325826</v>
       </c>
       <c r="B5" t="n">
-        <v>98587</v>
+        <v>98590</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 18032-2022 artfynd.xlsx
+++ b/artfynd/A 18032-2022 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>128329026</v>
       </c>
       <c r="B3" t="n">
-        <v>101898</v>
+        <v>101904</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>128329027</v>
       </c>
       <c r="B4" t="n">
-        <v>101898</v>
+        <v>101904</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>128325826</v>
       </c>
       <c r="B5" t="n">
-        <v>98590</v>
+        <v>98593</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 18032-2022 artfynd.xlsx
+++ b/artfynd/A 18032-2022 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>128329026</v>
       </c>
       <c r="B3" t="n">
-        <v>101904</v>
+        <v>101905</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>128329027</v>
       </c>
       <c r="B4" t="n">
-        <v>101904</v>
+        <v>101905</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>128325826</v>
       </c>
       <c r="B5" t="n">
-        <v>98593</v>
+        <v>98594</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 18032-2022 artfynd.xlsx
+++ b/artfynd/A 18032-2022 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>128329026</v>
       </c>
       <c r="B3" t="n">
-        <v>101905</v>
+        <v>101932</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>128329027</v>
       </c>
       <c r="B4" t="n">
-        <v>101905</v>
+        <v>101932</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>128325826</v>
       </c>
       <c r="B5" t="n">
-        <v>98594</v>
+        <v>98621</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 18032-2022 artfynd.xlsx
+++ b/artfynd/A 18032-2022 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>128329026</v>
       </c>
       <c r="B3" t="n">
-        <v>101932</v>
+        <v>101945</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>128329027</v>
       </c>
       <c r="B4" t="n">
-        <v>101932</v>
+        <v>101945</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>128325826</v>
       </c>
       <c r="B5" t="n">
-        <v>98621</v>
+        <v>98634</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 18032-2022 artfynd.xlsx
+++ b/artfynd/A 18032-2022 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>128329026</v>
       </c>
       <c r="B3" t="n">
-        <v>101945</v>
+        <v>101949</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>128329027</v>
       </c>
       <c r="B4" t="n">
-        <v>101945</v>
+        <v>101949</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>128325826</v>
       </c>
       <c r="B5" t="n">
-        <v>98634</v>
+        <v>98638</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 18032-2022 artfynd.xlsx
+++ b/artfynd/A 18032-2022 artfynd.xlsx
@@ -675,57 +675,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>80914658</v>
+        <v>128325826</v>
       </c>
       <c r="B2" t="n">
-        <v>99611</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99120</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221343</v>
+        <v>219811</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brunklöver</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Trifolium spadiceum</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>avk2019MITT870, Jmt</t>
+          <t>Artrik vägkant, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>432755.0601124244</v>
+        <v>433237</v>
       </c>
       <c r="R2" t="n">
-        <v>7059994.081745972</v>
+        <v>7060234</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -747,30 +742,19 @@
           <t>Offerdal</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-08-27</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2019-08-27</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Dikesbotten</t>
+          <t>NorraInneslänt (IS)Mika Thunell</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,12 +769,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Klas Andersson</t>
+          <t>Magnus Stenmark</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Klas Andersson, Magnus Sjölund</t>
+          <t>Magnus Stenmark</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -801,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128329026</v>
+        <v>80914658</v>
       </c>
       <c r="B3" t="n">
-        <v>101949</v>
+        <v>102464</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -831,22 +815,22 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Artrik vägkant, Jmt</t>
+          <t>avk2019MITT870, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>433249</v>
+        <v>432755</v>
       </c>
       <c r="R3" t="n">
-        <v>7060239</v>
+        <v>7059994</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -868,19 +852,20 @@
           <t>Offerdal</t>
         </is>
       </c>
+      <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2019-08-27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2019-08-27</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>NorraInneslänt (IS)Mika Thunell</t>
+          <t>Dikesbotten</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,12 +880,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Magnus Stenmark</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Stenmark</t>
+          <t>Klas Andersson, Magnus Sjölund</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -911,10 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128329027</v>
+        <v>128329026</v>
       </c>
       <c r="B4" t="n">
-        <v>101949</v>
+        <v>102464</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -950,10 +935,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>433234</v>
+        <v>433249</v>
       </c>
       <c r="R4" t="n">
-        <v>7060236</v>
+        <v>7060239</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1021,37 +1006,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128325826</v>
+        <v>128329027</v>
       </c>
       <c r="B5" t="n">
-        <v>98638</v>
+        <v>102464</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219811</v>
+        <v>221343</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Brunklöver</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Trifolium spadiceum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>500</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1060,10 +1045,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>433237</v>
+        <v>433234</v>
       </c>
       <c r="R5" t="n">
-        <v>7060234</v>
+        <v>7060236</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>

--- a/artfynd/A 18032-2022 artfynd.xlsx
+++ b/artfynd/A 18032-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -782,6 +787,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128325826</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -893,6 +903,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80914658</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1003,6 +1018,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128329026</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1113,8 +1133,19 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128329027</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>